--- a/downloads/TUVAT CVS Training - Sample Data File.xlsx
+++ b/downloads/TUVAT CVS Training - Sample Data File.xlsx
@@ -5,22 +5,27 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8b9aef44ae6f87e5/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xampp\htdocs\verify-cert-training\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{AB12DAB2-9309-424D-B06D-AEB2D319B6EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4256AE4D-2CE4-42AE-AD97-B664B7ECCA20}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC7D03F-53E3-4761-AEB1-C627691AD1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029" forceFullCalc="1"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="52">
   <si>
     <t>certificate_number</t>
   </si>
@@ -43,9 +48,6 @@
     <t>location</t>
   </si>
   <si>
-    <t>trainer</t>
-  </si>
-  <si>
     <t>training_date</t>
   </si>
   <si>
@@ -67,15 +69,6 @@
     <t>approval_by_email</t>
   </si>
   <si>
-    <t>TUVAT/CERT/2025/0528/112</t>
-  </si>
-  <si>
-    <t>TUVAT/CERT/2025/0528/113</t>
-  </si>
-  <si>
-    <t>TUVAT/CERT/2025/0528/114</t>
-  </si>
-  <si>
     <t>Test Participant 1</t>
   </si>
   <si>
@@ -130,9 +123,6 @@
     <t>Test Location 3</t>
   </si>
   <si>
-    <t>Test Trainer</t>
-  </si>
-  <si>
     <t>2025-06-16</t>
   </si>
   <si>
@@ -157,13 +147,40 @@
     <t>2027-06-20</t>
   </si>
   <si>
-    <t>am.sales@tuvat.com.bd</t>
-  </si>
-  <si>
-    <t>manager.ine@tuvat.com.bd</t>
-  </si>
-  <si>
-    <t>hse.ine01@tuvat.com.bd</t>
+    <t>certificate_type</t>
+  </si>
+  <si>
+    <t>Certificate</t>
+  </si>
+  <si>
+    <t>trainer_email</t>
+  </si>
+  <si>
+    <t>md.borhanuddin@tuvat.com.bd</t>
+  </si>
+  <si>
+    <t>Certificate of Competency</t>
+  </si>
+  <si>
+    <t>Certificate of Achievement</t>
+  </si>
+  <si>
+    <t>signatory_email</t>
+  </si>
+  <si>
+    <t>swad.mahfuz@tuvat.com.bd</t>
+  </si>
+  <si>
+    <t>TUVAT/CERT/2025/0713/001</t>
+  </si>
+  <si>
+    <t>TUVAT/CERT/2025/0713/002</t>
+  </si>
+  <si>
+    <t>TUVAT/CERT/2025/0713/003</t>
+  </si>
+  <si>
+    <t>afsana.akter@tuvat.com.bd</t>
   </si>
 </sst>
 </file>
@@ -515,212 +532,235 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P4"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:R4"/>
+  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.453125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.1796875" style="2"/>
-    <col min="9" max="9" width="12.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.81640625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.1796875" style="2"/>
+    <col min="1" max="1" width="18.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.88671875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.77734375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.21875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="R1" s="1"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1"/>
+      <c r="D2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="L3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K2" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="2" t="s">
+      <c r="O4" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>46</v>
+      <c r="Q4" s="2" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/downloads/TUVAT CVS Training - Sample Data File.xlsx
+++ b/downloads/TUVAT CVS Training - Sample Data File.xlsx
@@ -1,22 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xampp\htdocs\verify-cert-training\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC7D03F-53E3-4761-AEB1-C627691AD1EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A74E4168-FD0E-4952-94E9-E6B851B6D790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -25,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="55">
   <si>
     <t>certificate_number</t>
   </si>
@@ -181,6 +190,15 @@
   </si>
   <si>
     <t>afsana.akter@tuvat.com.bd</t>
+  </si>
+  <si>
+    <t>has_practical</t>
+  </si>
+  <si>
+    <t>is_refresher</t>
+  </si>
+  <si>
+    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -532,28 +550,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R4"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:T4"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.21875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.21875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.88671875" style="2" customWidth="1"/>
-    <col min="11" max="11" width="12.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.77734375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.77734375" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.21875" style="2"/>
+    <col min="1" max="1" width="18.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.85546875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.28515625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -561,53 +581,59 @@
         <v>40</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="1"/>
+      <c r="T1" s="1"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>48</v>
       </c>
@@ -615,105 +641,111 @@
         <v>41</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
@@ -721,45 +753,51 @@
         <v>45</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>47</v>
       </c>
     </row>

--- a/downloads/TUVAT CVS Training - Sample Data File.xlsx
+++ b/downloads/TUVAT CVS Training - Sample Data File.xlsx
@@ -1,31 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\xampp\htdocs\verify-cert-training\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A74E4168-FD0E-4952-94E9-E6B851B6D790}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D06C8439-F80B-4EC4-AE1F-62D1D277F914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -34,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="57">
   <si>
     <t>certificate_number</t>
   </si>
@@ -199,6 +190,12 @@
   </si>
   <si>
     <t>yes</t>
+  </si>
+  <si>
+    <t>internal_audit_training</t>
+  </si>
+  <si>
+    <t>online_training</t>
   </si>
 </sst>
 </file>
@@ -550,30 +547,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T4"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:V4"/>
+  <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.85546875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" style="2" customWidth="1"/>
-    <col min="15" max="15" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.28515625" style="2"/>
+    <col min="1" max="1" width="18.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.88671875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.6640625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -587,53 +586,59 @@
         <v>53</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="T1" s="1"/>
+      <c r="V1" s="1"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>48</v>
       </c>
@@ -644,52 +649,55 @@
         <v>54</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>49</v>
       </c>
@@ -699,53 +707,56 @@
       <c r="D3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="U3" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>50</v>
       </c>
@@ -758,46 +769,46 @@
       <c r="D4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="U4" s="2" t="s">
         <v>47</v>
       </c>
     </row>
